--- a/sheets/조재수대금교본/검수/대금 다스름.xlsx
+++ b/sheets/조재수대금교본/검수/대금 다스름.xlsx
@@ -1992,15 +1992,14 @@
       <c r="C4" s="23"/>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽林仲
+          <t xml:space="preserve">林仲
 –</t>
         </is>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ
-∽
+          <t xml:space="preserve">湳
 –
 –</t>
         </is>
@@ -2008,7 +2007,7 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>
@@ -2017,8 +2016,8 @@
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-ʒ潢㳞
-汰∽</t>
+潢㳞
+汰</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -2028,14 +2027,14 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И</t>
+–</t>
         </is>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–林ʒ</t>
+–林</t>
         </is>
       </c>
       <c r="E5" s="27"/>
@@ -2043,7 +2042,7 @@
         <is>
           <t xml:space="preserve">–
 –
-ʒ淋汰∽</t>
+淋汰</t>
         </is>
       </c>
       <c r="G5" s="26"/>
@@ -2051,7 +2050,7 @@
         <is>
           <t xml:space="preserve">–
 –
-汰ʒ</t>
+汰</t>
         </is>
       </c>
       <c r="I5" s="26"/>
@@ -2063,14 +2062,14 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞∼
-–И</t>
+–</t>
         </is>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢∼
-–И</t>
+–</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2085,16 +2084,16 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋∼
-–է
-湳淋ʒ</t>
+–
+湳淋</t>
         </is>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰∧
-ʒ潢南</t>
+–汰
+潢南</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -2104,40 +2103,38 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰淋
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–ㄴ∼
-ʒ潢㳞⊏</t>
+–∼
+潢㳞</t>
         </is>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞⊏
-–汰∽
-ʒ潢南</t>
+          <t xml:space="preserve">㳞
+–汰
+潢南</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ
-ʒ潢㳞⊏</t>
+–
+潢㳞</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -2146,21 +2143,21 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-∽林仲</t>
+          <t xml:space="preserve">潢
+林仲</t>
         </is>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃∼
-–И</t>
+–</t>
         </is>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ∽汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>
@@ -2176,7 +2173,7 @@
       <c r="I8" s="26"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>
@@ -2194,7 +2191,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽林仲
+          <t xml:space="preserve">林仲
 黃仲</t>
         </is>
       </c>
@@ -2210,8 +2207,8 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–ㄴ∼
-ʒ潢㳞</t>
+–∼
+潢㳞</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -2228,15 +2225,15 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ潢㳞
-汰ʒ</t>
+          <t xml:space="preserve">潢㳞
+汰</t>
         </is>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林無
-⊏∼
+∼
 –林</t>
         </is>
       </c>
@@ -2245,7 +2242,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ∽汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>

--- a/sheets/조재수대금교본/검수/대금 다스름.xlsx
+++ b/sheets/조재수대금교본/검수/대금 다스름.xlsx
@@ -1992,14 +1992,15 @@
       <c r="C4" s="23"/>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">林仲
+          <t xml:space="preserve">∽林仲
 –</t>
         </is>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳ㄱ
+∽
 –
 –</t>
         </is>
@@ -2007,7 +2008,7 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 –
 –</t>
         </is>
@@ -2016,8 +2017,8 @@
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-潢㳞
-汰</t>
+ʒ潢㳞
+汰∽</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -2027,14 +2028,14 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–И</t>
         </is>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–林</t>
+–林ʒ</t>
         </is>
       </c>
       <c r="E5" s="27"/>
@@ -2042,7 +2043,7 @@
         <is>
           <t xml:space="preserve">–
 –
-淋汰</t>
+ʒ淋汰∽</t>
         </is>
       </c>
       <c r="G5" s="26"/>
@@ -2050,7 +2051,7 @@
         <is>
           <t xml:space="preserve">–
 –
-汰</t>
+汰ʒ</t>
         </is>
       </c>
       <c r="I5" s="26"/>
@@ -2062,14 +2063,14 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞∼
-–</t>
+–И</t>
         </is>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢∼
-–</t>
+–И</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2084,16 +2085,16 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋∼
-–
-湳淋</t>
+–է
+湳淋ʒ</t>
         </is>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰
-潢南</t>
+–汰∧
+ʒ潢南</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -2103,38 +2104,38 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰淋
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–∼
-潢㳞</t>
+–ㄴ∼
+ʒ潢㳞⊏</t>
         </is>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-–汰
-潢南</t>
+          <t xml:space="preserve">㳞⊏
+–汰∽
+ʒ潢南</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–
-潢㳞</t>
+–ㄴ
+ʒ潢㳞⊏</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -2143,21 +2144,21 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-林仲</t>
+          <t xml:space="preserve">潢ʒ
+∽林仲</t>
         </is>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃∼
-–</t>
+–И</t>
         </is>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">ʒ∽汰潢
 –
 –</t>
         </is>
@@ -2173,7 +2174,7 @@
       <c r="I8" s="26"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">ʒ汰潢
 –
 –</t>
         </is>
@@ -2191,7 +2192,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林仲
+          <t xml:space="preserve">∽林仲
 黃仲</t>
         </is>
       </c>
@@ -2207,8 +2208,8 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–∼
-潢㳞</t>
+–ㄴ∼
+ʒ潢㳞</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -2225,15 +2226,15 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
-汰</t>
+          <t xml:space="preserve">ʒ潢㳞
+汰ʒ</t>
         </is>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林無
-∼
+⊏∼
 –林</t>
         </is>
       </c>
@@ -2242,7 +2243,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">ʒ∽汰潢
 –
 –</t>
         </is>

--- a/sheets/조재수대금교본/검수/대금 다스름.xlsx
+++ b/sheets/조재수대금교본/검수/대금 다스름.xlsx
@@ -2256,7 +2256,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢○
+          <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/대금 다스름.xlsx
+++ b/sheets/조재수대금교본/검수/대금 다스름.xlsx
@@ -1936,22 +1936,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="100.0" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="149.15" customHeight="true">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -1981,7 +1981,7 @@
       <c r="J3" s="21"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="149.15" customHeight="true">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="149.15" customHeight="true">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="26"/>
     </row>
-    <row r="6" ht="149.15" customHeight="true">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" ht="149.15" customHeight="true">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" ht="149.15" customHeight="true">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K8" s="26"/>
     </row>
-    <row r="9" ht="149.15" customHeight="true">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" ht="149.15" customHeight="true">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" ht="149.15" customHeight="true">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       <c r="J11" s="21"/>
       <c r="K11" s="26"/>
     </row>
-    <row r="12" ht="149.15" customHeight="true">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -2293,7 +2293,7 @@
       <c r="J12" s="21"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" ht="149.15" customHeight="true">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="149.15" customHeight="true">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -2333,6 +2333,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="40"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
 </worksheet>
 </file>